--- a/easyData.xlsx
+++ b/easyData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\廖雨潔\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A445EFEC-00E1-48D4-BDDD-DF79BADDC120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE24896-6465-48F8-AD5A-94AD80791732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="861" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="681">
   <si>
     <t>activeScence</t>
   </si>
@@ -544,16 +544,7 @@
     <t>麵包店</t>
   </si>
   <si>
-    <t>balcony</t>
-  </si>
-  <si>
-    <t>陽台</t>
-  </si>
-  <si>
     <t>basement</t>
-  </si>
-  <si>
-    <t>地下室</t>
   </si>
   <si>
     <t>bedroom</t>
@@ -602,15 +593,6 @@
     <t>garage</t>
   </si>
   <si>
-    <t>車庫</t>
-  </si>
-  <si>
-    <t>hall</t>
-  </si>
-  <si>
-    <t>大廳</t>
-  </si>
-  <si>
     <t>hospital</t>
   </si>
   <si>
@@ -923,12 +905,6 @@
     <t>小考</t>
   </si>
   <si>
-    <t>record</t>
-  </si>
-  <si>
-    <t>紀錄</t>
-  </si>
-  <si>
     <t>ruler</t>
   </si>
   <si>
@@ -986,16 +962,7 @@
     <t>課本</t>
   </si>
   <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>標題</t>
-  </si>
-  <si>
     <t>topic</t>
-  </si>
-  <si>
-    <t>主題</t>
   </si>
   <si>
     <t>vocabulary</t>
@@ -1074,18 +1041,6 @@
     <t>store</t>
   </si>
   <si>
-    <t>We go swimming on hot days at the _______.</t>
-  </si>
-  <si>
-    <t>Tom waits for the train at the _______.</t>
-  </si>
-  <si>
-    <t>Amy likes reading, so she goes to the _______.</t>
-  </si>
-  <si>
-    <t>Dad keeps his car in the _______.</t>
-  </si>
-  <si>
     <t>The teacher writes on the board in the _______.</t>
   </si>
   <si>
@@ -1324,9 +1279,6 @@
   </si>
   <si>
     <t>Where can you keep your money safely?</t>
-  </si>
-  <si>
-    <t>Where can you see many tall offices together?</t>
   </si>
   <si>
     <t>Where do people go to pray on Sundays?</t>
@@ -2187,6 +2139,46 @@
   </si>
   <si>
     <t xml:space="preserve">Tom writes </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bookcase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shirt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skirt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shoes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>socks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>We go swimming on hot days at the _______.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dad keeps his car in the ______.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tom waits for the train at the _______.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amy likes reading, so she goes to the _______.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>building_sorting</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2594,7 +2586,7 @@
         <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="D2" t="s">
         <v>37</v>
@@ -2608,7 +2600,7 @@
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>556</v>
+        <v>680</v>
       </c>
       <c r="D3" t="s">
         <v>38</v>
@@ -2622,7 +2614,7 @@
         <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="D4" t="s">
         <v>41</v>
@@ -2636,7 +2628,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>558</v>
+        <v>539</v>
       </c>
       <c r="D5" t="s">
         <v>37</v>
@@ -2650,7 +2642,7 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>557</v>
+        <v>540</v>
       </c>
       <c r="D6" t="s">
         <v>38</v>
@@ -2703,10 +2695,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>52</v>
+        <v>434</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>66</v>
@@ -2723,16 +2715,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>48</v>
+        <v>435</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>78</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>60</v>
+        <v>674</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>48</v>
@@ -2743,10 +2735,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>60</v>
+        <v>436</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>80</v>
@@ -2763,16 +2755,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>90</v>
+        <v>437</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>96</v>
+        <v>673</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>90</v>
@@ -2783,10 +2775,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>66</v>
+        <v>438</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>48</v>
@@ -2803,10 +2795,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>455</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>50</v>
+        <v>439</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>60</v>
@@ -2823,10 +2815,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>456</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>110</v>
+        <v>440</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>55</v>
@@ -2843,10 +2835,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>457</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>57</v>
+        <v>441</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>675</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>100</v>
@@ -2863,10 +2855,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>458</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>88</v>
+        <v>442</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>82</v>
@@ -2883,10 +2875,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>86</v>
+        <v>443</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>52</v>
@@ -2903,10 +2895,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>108</v>
+        <v>444</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>94</v>
@@ -2923,10 +2915,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>64</v>
+        <v>445</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>58</v>
@@ -2943,10 +2935,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>98</v>
+        <v>446</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>82</v>
@@ -2963,10 +2955,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>106</v>
+        <v>672</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>100</v>
@@ -2981,6 +2973,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3021,19 +3014,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>195</v>
+        <v>412</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>255</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -3041,10 +3034,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>429</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>144</v>
+        <v>413</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>261</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>151</v>
@@ -3061,19 +3054,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>216</v>
+        <v>414</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>263</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -3081,19 +3074,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>241</v>
+        <v>415</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>265</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>243</v>
+        <v>671</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -3101,19 +3094,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>255</v>
+        <v>416</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>303</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -3121,19 +3114,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>313</v>
+        <v>417</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>268</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>434</v>
+        <v>418</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -3141,19 +3134,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>288</v>
+        <v>419</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>270</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -3161,19 +3154,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>214</v>
+        <v>421</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>274</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>124</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -3181,19 +3174,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>251</v>
+        <v>423</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>276</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -3201,19 +3194,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>309</v>
+        <v>425</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>278</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -3221,19 +3214,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>195</v>
+        <v>426</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>286</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -3241,19 +3234,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>280</v>
+        <v>429</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>293</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>122</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -3261,19 +3254,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>284</v>
+        <v>430</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>295</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -3281,19 +3274,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>249</v>
+        <v>432</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>300</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -3301,19 +3294,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>449</v>
+        <v>433</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>305</v>
+        <v>671</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>134</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -3363,7 +3356,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>330</v>
+        <v>678</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>144</v>
@@ -3372,7 +3365,7 @@
         <v>134</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>147</v>
@@ -3384,19 +3377,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>331</v>
+        <v>679</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>151</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="G3" s="4"/>
     </row>
@@ -3405,19 +3398,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>332</v>
+        <v>677</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>138</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -3426,16 +3419,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>329</v>
+        <v>676</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>138</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>138</v>
@@ -3447,19 +3440,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>126</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="G6" s="4"/>
     </row>
@@ -3468,19 +3461,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>136</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G7" s="4"/>
     </row>
@@ -3489,13 +3482,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>126</v>
@@ -3510,7 +3503,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>155</v>
@@ -3531,7 +3524,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>151</v>
@@ -3540,7 +3533,7 @@
         <v>132</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>151</v>
@@ -3552,16 +3545,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>153</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>153</v>
@@ -3573,13 +3566,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>132</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>138</v>
@@ -3594,13 +3587,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>126</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>144</v>
@@ -3615,16 +3608,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>114</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>114</v>
@@ -3636,7 +3629,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>122</v>
@@ -3645,7 +3638,7 @@
         <v>151</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>122</v>
@@ -3657,16 +3650,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>120</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>120</v>
@@ -3678,19 +3671,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>151</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -3698,19 +3691,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>126</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -3718,19 +3711,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>134</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -3738,10 +3731,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>147</v>
@@ -3750,7 +3743,7 @@
         <v>132</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -3758,10 +3751,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>120</v>
@@ -3770,7 +3763,7 @@
         <v>138</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -3808,12 +3801,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="97.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>52</v>
@@ -3828,12 +3821,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="81" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>110</v>
@@ -3848,12 +3841,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="81" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>57</v>
@@ -3868,12 +3861,12 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="113.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>55</v>
@@ -3888,12 +3881,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="113.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>66</v>
@@ -3908,12 +3901,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="113.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>100</v>
@@ -3928,12 +3921,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="81" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>108</v>
@@ -3948,12 +3941,12 @@
         <v>108</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="97.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>64</v>
@@ -3968,12 +3961,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="97.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>88</v>
@@ -3988,12 +3981,12 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="97.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>90</v>
@@ -4008,12 +4001,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="97.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>104</v>
@@ -4028,12 +4021,12 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="113.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>108</v>
@@ -4048,12 +4041,12 @@
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="113.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>52</v>
@@ -4068,12 +4061,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="64.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>102</v>
@@ -4088,12 +4081,12 @@
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="97.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>78</v>
@@ -4108,12 +4101,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="97.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>94</v>
@@ -4128,32 +4121,32 @@
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="113.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>98</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>82</v>
@@ -4168,12 +4161,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="113.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>86</v>
@@ -4188,15 +4181,15 @@
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="64.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>92</v>
@@ -4205,7 +4198,7 @@
         <v>84</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -4242,195 +4235,195 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="81" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="97.2" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>132</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="81" x14ac:dyDescent="0.3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="113.4" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>124</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="81" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="81" x14ac:dyDescent="0.3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="97.2" x14ac:dyDescent="0.3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="97.2" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>124</v>
@@ -4439,75 +4432,75 @@
         <v>126</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="64.8" x14ac:dyDescent="0.3">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>151</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="97.2" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="97.2" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>96</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="97.2" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>26</v>
@@ -4516,130 +4509,130 @@
         <v>130</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>151</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="97.2" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="97.2" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>134</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="97.2" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>60</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="113.4" x14ac:dyDescent="0.3">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="81" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -4685,16 +4678,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>546</v>
+        <v>530</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>482</v>
+        <v>466</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>483</v>
+        <v>467</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -4702,16 +4695,16 @@
         <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -4719,16 +4712,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>487</v>
+        <v>471</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -4736,16 +4729,16 @@
         <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>540</v>
+        <v>524</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>539</v>
+        <v>523</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>481</v>
+        <v>465</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -4753,16 +4746,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>489</v>
+        <v>473</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>490</v>
+        <v>474</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -4770,16 +4763,16 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -4787,16 +4780,16 @@
         <v>7</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>536</v>
+        <v>520</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>494</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -4804,16 +4797,16 @@
         <v>8</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>533</v>
+        <v>517</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -4821,16 +4814,16 @@
         <v>9</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>531</v>
+        <v>515</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>498</v>
+        <v>482</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -4838,16 +4831,16 @@
         <v>10</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>500</v>
+        <v>484</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -4855,16 +4848,16 @@
         <v>11</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>503</v>
+        <v>487</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -4872,16 +4865,16 @@
         <v>12</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>505</v>
+        <v>489</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -4889,16 +4882,16 @@
         <v>13</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>554</v>
+        <v>538</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>552</v>
+        <v>536</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>506</v>
+        <v>490</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -4906,16 +4899,16 @@
         <v>14</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>507</v>
+        <v>491</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -4923,16 +4916,16 @@
         <v>15</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>477</v>
+        <v>461</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>509</v>
+        <v>493</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -4940,16 +4933,16 @@
         <v>16</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>512</v>
+        <v>496</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -4957,16 +4950,16 @@
         <v>17</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>525</v>
+        <v>509</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>526</v>
+        <v>510</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>513</v>
+        <v>497</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -4974,16 +4967,16 @@
         <v>18</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>514</v>
+        <v>498</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>516</v>
+        <v>500</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -4991,16 +4984,16 @@
         <v>19</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>518</v>
+        <v>502</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>519</v>
+        <v>503</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -5008,16 +5001,16 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>521</v>
+        <v>505</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>522</v>
+        <v>506</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>520</v>
+        <v>504</v>
       </c>
     </row>
   </sheetData>
@@ -5063,16 +5056,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>560</v>
+        <v>544</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>561</v>
+        <v>545</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -5080,16 +5073,16 @@
         <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>562</v>
+        <v>546</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>563</v>
+        <v>547</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>564</v>
+        <v>548</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -5097,16 +5090,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>565</v>
+        <v>549</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>566</v>
+        <v>550</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>567</v>
+        <v>551</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -5114,16 +5107,16 @@
         <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>568</v>
+        <v>552</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>569</v>
+        <v>553</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>570</v>
+        <v>554</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -5131,16 +5124,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>572</v>
+        <v>556</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>573</v>
+        <v>557</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -5148,16 +5141,16 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>568</v>
+        <v>552</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>574</v>
+        <v>558</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>575</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -5165,16 +5158,16 @@
         <v>7</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>576</v>
+        <v>560</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>577</v>
+        <v>561</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>578</v>
+        <v>562</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -5182,16 +5175,16 @@
         <v>8</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>579</v>
+        <v>563</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>580</v>
+        <v>564</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>581</v>
+        <v>565</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -5199,16 +5192,16 @@
         <v>9</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>568</v>
+        <v>552</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>582</v>
+        <v>566</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>583</v>
+        <v>567</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -5216,16 +5209,16 @@
         <v>10</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>584</v>
+        <v>568</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>568</v>
+        <v>552</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>585</v>
+        <v>569</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>586</v>
+        <v>570</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -5233,16 +5226,16 @@
         <v>11</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>587</v>
+        <v>571</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>588</v>
+        <v>572</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>589</v>
+        <v>573</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>590</v>
+        <v>574</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -5250,16 +5243,16 @@
         <v>12</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>593</v>
+        <v>577</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>594</v>
+        <v>578</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -5267,16 +5260,16 @@
         <v>13</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>595</v>
+        <v>579</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>596</v>
+        <v>580</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>597</v>
+        <v>581</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -5284,16 +5277,16 @@
         <v>14</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>568</v>
+        <v>552</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>598</v>
+        <v>582</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>599</v>
+        <v>583</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -5301,16 +5294,16 @@
         <v>15</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -5318,16 +5311,16 @@
         <v>16</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>603</v>
+        <v>587</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>604</v>
+        <v>588</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>605</v>
+        <v>589</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>606</v>
+        <v>590</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -5335,16 +5328,16 @@
         <v>17</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>607</v>
+        <v>591</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>568</v>
+        <v>552</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>608</v>
+        <v>592</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>609</v>
+        <v>593</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -5352,16 +5345,16 @@
         <v>18</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>610</v>
+        <v>594</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>612</v>
+        <v>596</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>613</v>
+        <v>597</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -5369,16 +5362,16 @@
         <v>19</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>614</v>
+        <v>598</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -5386,16 +5379,16 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>616</v>
+        <v>600</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>619</v>
+        <v>603</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>618</v>
+        <v>602</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>617</v>
+        <v>601</v>
       </c>
     </row>
   </sheetData>
@@ -5441,16 +5434,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>686</v>
+        <v>670</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>685</v>
+        <v>669</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>620</v>
+        <v>604</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>621</v>
+        <v>605</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -5458,16 +5451,16 @@
         <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>622</v>
+        <v>606</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>623</v>
+        <v>607</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>624</v>
+        <v>608</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -5475,16 +5468,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>625</v>
+        <v>609</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>626</v>
+        <v>610</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>627</v>
+        <v>611</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -5492,16 +5485,16 @@
         <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>628</v>
+        <v>612</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>629</v>
+        <v>613</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>630</v>
+        <v>614</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -5509,16 +5502,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>631</v>
+        <v>615</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>633</v>
+        <v>617</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -5526,16 +5519,16 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>634</v>
+        <v>618</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>635</v>
+        <v>619</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>636</v>
+        <v>620</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -5543,16 +5536,16 @@
         <v>7</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>637</v>
+        <v>621</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>638</v>
+        <v>622</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>639</v>
+        <v>623</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -5560,16 +5553,16 @@
         <v>8</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>640</v>
+        <v>624</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>641</v>
+        <v>625</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>642</v>
+        <v>626</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -5577,16 +5570,16 @@
         <v>9</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>643</v>
+        <v>627</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>644</v>
+        <v>628</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>645</v>
+        <v>629</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>646</v>
+        <v>630</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -5594,16 +5587,16 @@
         <v>10</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>647</v>
+        <v>631</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>648</v>
+        <v>632</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>649</v>
+        <v>633</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>650</v>
+        <v>634</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -5611,16 +5604,16 @@
         <v>11</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>595</v>
+        <v>579</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>652</v>
+        <v>636</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>653</v>
+        <v>637</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -5628,16 +5621,16 @@
         <v>12</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>654</v>
+        <v>638</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>655</v>
+        <v>639</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>656</v>
+        <v>640</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>657</v>
+        <v>641</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -5645,16 +5638,16 @@
         <v>13</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>658</v>
+        <v>642</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>659</v>
+        <v>643</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>660</v>
+        <v>644</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>597</v>
+        <v>581</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -5662,16 +5655,16 @@
         <v>14</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>661</v>
+        <v>645</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>662</v>
+        <v>646</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>663</v>
+        <v>647</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>664</v>
+        <v>648</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -5679,16 +5672,16 @@
         <v>15</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>607</v>
+        <v>591</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>665</v>
+        <v>649</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>666</v>
+        <v>650</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>667</v>
+        <v>651</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -5696,16 +5689,16 @@
         <v>16</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>668</v>
+        <v>652</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>669</v>
+        <v>653</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>670</v>
+        <v>654</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>671</v>
+        <v>655</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -5713,16 +5706,16 @@
         <v>17</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>672</v>
+        <v>656</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>673</v>
+        <v>657</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -5730,16 +5723,16 @@
         <v>18</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>587</v>
+        <v>571</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>677</v>
+        <v>661</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>678</v>
+        <v>662</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -5747,16 +5740,16 @@
         <v>19</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>679</v>
+        <v>663</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>681</v>
+        <v>665</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -5764,16 +5757,16 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>682</v>
+        <v>666</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
     </row>
   </sheetData>
@@ -6026,7 +6019,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39E98AFF-E280-424F-B2C7-103782CACFE5}">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="23.44140625" style="3" customWidth="1"/>
@@ -6234,7 +6227,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>146</v>
@@ -6300,10 +6293,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -6311,10 +6304,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -6322,10 +6315,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -6333,10 +6326,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -6344,10 +6337,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -6355,10 +6348,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -6366,10 +6359,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -6377,10 +6370,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -6388,10 +6381,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -6399,10 +6392,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -6410,10 +6403,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -6421,10 +6414,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -6432,10 +6425,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -6443,10 +6436,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -6454,59 +6447,15 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6626,7 +6575,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>58</v>
+        <v>672</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>59</v>
@@ -6742,7 +6691,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -6885,7 +6834,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -6930,7 +6879,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D57D8C-95C2-4DBD-AE75-10E382385048}">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15" style="3" customWidth="1"/>
@@ -6959,498 +6908,474 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" s="2" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B30" s="2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B32" s="2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B33" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B34" s="2" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B35" s="2" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B36" s="2" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B37" s="2" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B38" s="2" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B39" s="2" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B40" s="2" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B41" s="2" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B42" s="2" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B43" s="2" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B44" s="2" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B45" s="2" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B46" s="2" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B47" s="2" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B48" s="2" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B49" s="2" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B50" s="2" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B51" s="2" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B52" s="2" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B53" s="2" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B54" s="2" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B55" s="2" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B56" s="2" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B57" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B58" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B59" s="2" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B60" s="2" t="s">
-        <v>307</v>
+        <v>237</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B61" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B62" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B63" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -7493,10 +7418,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -7504,10 +7429,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -7515,10 +7440,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -7526,10 +7451,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -7537,10 +7462,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -7548,10 +7473,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -7559,10 +7484,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -7570,10 +7495,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -7581,10 +7506,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -7592,10 +7517,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -7603,7 +7528,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>114</v>
@@ -7614,7 +7539,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>116</v>
@@ -7625,7 +7550,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>122</v>
@@ -7636,7 +7561,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>134</v>
@@ -7647,7 +7572,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>136</v>
@@ -7658,7 +7583,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>151</v>
@@ -7669,7 +7594,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>155</v>
@@ -7680,10 +7605,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -7691,10 +7616,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -7702,10 +7627,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -7751,7 +7676,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>120</v>
@@ -7762,7 +7687,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>122</v>
@@ -7773,7 +7698,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>130</v>
@@ -7784,7 +7709,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>136</v>
@@ -7795,10 +7720,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -7806,10 +7731,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -7817,10 +7742,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -7828,7 +7753,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>151</v>
@@ -7839,7 +7764,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>153</v>
@@ -7850,10 +7775,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -7861,7 +7786,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>46</v>
@@ -7872,7 +7797,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>48</v>
@@ -7883,7 +7808,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>50</v>
@@ -7894,7 +7819,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>52</v>
@@ -7905,7 +7830,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>53</v>
@@ -7916,7 +7841,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>55</v>
@@ -7927,7 +7852,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>57</v>
@@ -7938,7 +7863,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>58</v>
@@ -7949,7 +7874,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>60</v>
@@ -7960,7 +7885,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>62</v>
@@ -8015,7 +7940,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>82</v>
@@ -8026,7 +7951,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>84</v>
@@ -8037,7 +7962,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>86</v>
@@ -8048,7 +7973,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>88</v>
@@ -8059,7 +7984,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>90</v>
@@ -8070,7 +7995,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>92</v>
@@ -8081,7 +8006,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>94</v>
@@ -8092,7 +8017,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>96</v>
@@ -8103,7 +8028,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>98</v>
@@ -8114,7 +8039,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>100</v>
@@ -8125,10 +8050,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -8136,10 +8061,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -8147,10 +8072,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -8158,10 +8083,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -8169,10 +8094,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -8180,10 +8105,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -8191,10 +8116,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -8202,10 +8127,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -8213,10 +8138,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -8224,10 +8149,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -8247,7 +8172,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="53.77734375" customWidth="1"/>
@@ -8282,16 +8207,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>134</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>114</v>
@@ -8302,7 +8227,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>126</v>
@@ -8314,287 +8239,267 @@
         <v>151</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>118</v>
+        <v>398</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>120</v>
+        <v>399</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>138</v>
+        <v>181</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>151</v>
+        <v>400</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>153</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>187</v>
+        <v>317</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>151</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>122</v>
+        <v>401</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>161</v>
+        <v>403</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>158</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>418</v>
+        <v>179</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>419</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>179</v>
+        <v>404</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>160</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>185</v>
+        <v>126</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>183</v>
+        <v>405</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>191</v>
+        <v>138</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>421</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>167</v>
+        <v>406</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>136</v>
+        <v>407</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>175</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>120</v>
+        <v>185</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>138</v>
+        <v>408</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>155</v>
+        <v>409</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>425</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>147</v>
+        <v>410</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>153</v>
+        <v>319</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>147</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="C16" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>187</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>132</v>
+        <v>314</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>334</v>
+        <v>175</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
